--- a/outputs/finance-hours-2026-10-22/finance-time-decomposition.xlsx
+++ b/outputs/finance-hours-2026-10-22/finance-time-decomposition.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Підсумок" sheetId="1" r:id="R778e227e6f6b44c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Декомпозиція" sheetId="2" r:id="Rcb8fe0d830ed4fff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Підсумок" sheetId="1" r:id="R9a41bba85e7c4716"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Декомпозиція" sheetId="2" r:id="R796b34f319a54438"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Методика" sheetId="3" r:id="R1ec2312ade8b4d45"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -58,7 +59,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="7">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -83,6 +84,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF233F5B"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -116,7 +122,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="43">
+  <x:cellXfs count="49">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -241,6 +247,24 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1559,7 +1583,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdacc5754341b48ec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1f61ec0353a493f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5756,7 +5780,199 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda2708975a3b4fda"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c7b91f14fcf4629"/>
   </x:tableParts>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF70839A"/>
+  </x:sheetPr>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="35" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="105" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="25" customHeight="1">
+      <x:c r="A1" s="2"/>
+      <x:c r="B1" s="2"/>
+    </x:row>
+    <x:row r="2" ht="25" customHeight="1">
+      <x:c r="A2" s="3" t="str">
+        <x:v>Методика оцінювання годин</x:v>
+      </x:c>
+      <x:c r="B2" s="2"/>
+    </x:row>
+    <x:row r="3" ht="25" customHeight="1">
+      <x:c r="A3" s="4" t="str">
+        <x:v>Опис додано 25.10.2026. Планові оцінки зберігаються станом на 22.10.2026.</x:v>
+      </x:c>
+      <x:c r="B3" s="2"/>
+    </x:row>
+    <x:row r="4" ht="25" customHeight="1">
+      <x:c r="A4" s="2"/>
+      <x:c r="B4" s="2"/>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5" s="45" t="str">
+        <x:v>Питання</x:v>
+      </x:c>
+      <x:c r="B5" s="45" t="str">
+        <x:v>Як оцінювали</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="46" customHeight="1">
+      <x:c r="A6" s="47" t="str">
+        <x:v>Метод</x:v>
+      </x:c>
+      <x:c r="B6" s="48" t="str">
+        <x:v>Оцінювання знизу вгору (bottom-up): кожну фічу розбито на технічні підзадачі, кожну оцінено окремо, потім підсумовано. Це експертне судження після аналізу коду, не виміряна продуктивність.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="46" customHeight="1">
+      <x:c r="A7" s="47" t="str">
+        <x:v>Вихідна база</x:v>
+      </x:c>
+      <x:c r="B7" s="48" t="str">
+        <x:v>Переглянуто імпортер, звіт, категорії, Beancount, структуру й установлені залежності. Рахували залишок роботи до погодженого результату, з повторним використанням готових компонентів.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="46" customHeight="1">
+      <x:c r="A8" s="47" t="str">
+        <x:v>A — реалізація з Codex</x:v>
+      </x:c>
+      <x:c r="B8" s="48" t="str">
+        <x:v>Активний час розробника: уточнення підзадачі, продуктове рішення, постановка задачі Codex, читання та інтеграція коду. Автономний час моделі не додається як окрема людино-година.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="46" customHeight="1">
+      <x:c r="A9" s="47" t="str">
+        <x:v>B — перевірка людиною</x:v>
+      </x:c>
+      <x:c r="B9" s="48" t="str">
+        <x:v>Перегляд результатів Codex, запуск тестів, ручна звірка сум і прав доступу, аналіз помилок, повторна перевірка. Якщо виправлення виділено окремим рядком, вони не включені вдруге в інші рядки.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="46" customHeight="1">
+      <x:c r="A10" s="47" t="str">
+        <x:v>Формула підзадачі</x:v>
+      </x:c>
+      <x:c r="B10" s="48" t="str">
+        <x:v>Для поточної оцінки t = A + B. Наприклад, підзадача 2.2: 2 год реалізації + 1 год перевірки = 3 год. Сума фічі — сума всіх її підзадач.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="46" customHeight="1">
+      <x:c r="A11" s="47" t="str">
+        <x:v>Звідки 0,5 / 1 / 1,5 / 3 год</x:v>
+      </x:c>
+      <x:c r="B11" s="48" t="str">
+        <x:v>Це планові блоки з кроком 0,5 год. Враховано обсяг змін, фінансову складність, залежності, наявний код і перелік перевірок. Хронометражу чи статистики швидкості Codex немає; точність до півгодини умовна.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="46" customHeight="1">
+      <x:c r="A12" s="47" t="str">
+        <x:v>Що дає Codex</x:v>
+      </x:c>
+      <x:c r="B12" s="48" t="str">
+        <x:v>Допомагає писати, аналізувати й виправляти код. Фіксованої знижки на години або припущення «у кілька разів швидше» немає. Рішення, перевірка даних і приймання залишаються за людиною.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="46" customHeight="1">
+      <x:c r="A13" s="47" t="str">
+        <x:v>Готовий код і залежності</x:v>
+      </x:c>
+      <x:c r="B13" s="48" t="str">
+        <x:v>Повторно використовуємо парсер Олі, Decimal, правила категорій і адаптивний звіт. Оцінка фічі діє після готових передумов. Наприклад, 4,5 год подушки не включають повторну розробку входу чи сховища.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="46" customHeight="1">
+      <x:c r="A14" s="47" t="str">
+        <x:v>Спільні години</x:v>
+      </x:c>
+      <x:c r="B14" s="48" t="str">
+        <x:v>S0 — модель і зберігання; G-M — спільна інтеграція Must; G-S/G-C — перевірки додаткових пакетів. Кожен блок включається один раз. Перевірки стиків відрізняються від локальних тестів фіч.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="46" customHeight="1">
+      <x:c r="A15" s="47" t="str">
+        <x:v>Фінансові залежності</x:v>
+      </x:c>
+      <x:c r="B15" s="48" t="str">
+        <x:v>№19, повторний імпорт, входить у №2. №20, правила часток, і №22, погашення, входять у №9. Окремих дубльованих годин на ці можливості немає.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="46" customHeight="1">
+      <x:c r="A16" s="47" t="str">
+        <x:v>Резерв</x:v>
+      </x:c>
+      <x:c r="B16" s="48" t="str">
+        <x:v>Частка резерву задається в «Підсумок», B10. Повний план = відома робота / (1 − частка резерву). За 25%: 98,5 / 0,75 = 131,33 год, з них 32,83 год резерву. Це приклад початкового плану від 22.10.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="46" customHeight="1">
+      <x:c r="A17" s="47" t="str">
+        <x:v>Що покриває резерв</x:v>
+      </x:c>
+      <x:c r="B17" s="48" t="str">
+        <x:v>Лише невідомі складнощі понад описані підзадачі. Відомі перевірки, перегляд Codex і виправлення вже включені в A/B. Нову відому роботу оцінюємо окремо, а не приховуємо в резерві.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="46" customHeight="1">
+      <x:c r="A18" s="47" t="str">
+        <x:v>Історичні оцінки Won’t</x:v>
+      </x:c>
+      <x:c r="B18" s="48" t="str">
+        <x:v>Початкові години збережені для довідки, не переоцінені під Supabase/PWA. Поділ на A/B невідомий і залишений порожнім. Ці фічі не додаються до активних пакетів. №7 і №18 мають умовні нижні межі.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="46" customHeight="1">
+      <x:c r="A19" s="47" t="str">
+        <x:v>Пріоритети й оцінка часу</x:v>
+      </x:c>
+      <x:c r="B19" s="48" t="str">
+        <x:v>MoSCoW визначає обсяг версії, Value vs Effort порівнює користь і зусилля. Ці методи не обчислюють тривалість реалізації. Години отримані з декомпозиції, а потім використані для пріоритизації.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="46" customHeight="1">
+      <x:c r="A20" s="47" t="str">
+        <x:v>Години й календар</x:v>
+      </x:c>
+      <x:c r="B20" s="48" t="str">
+        <x:v>Рахуємо активний час розробника, не хвилини внесення витрат у трекер. Календарний строк залежить від доступних годин на тиждень. Очікування схвалення або відповіді провайдера не прирівнюється до активних годин.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="46" customHeight="1">
+      <x:c r="A21" s="47" t="str">
+        <x:v>Як уточнювати оцінки</x:v>
+      </x:c>
+      <x:c r="B21" s="48" t="str">
+        <x:v>Після перших завершених підзадач записати фактичні A/B, порівняти з планом і переоцінити схожі майбутні задачі. Нові вимоги змінюють обсяг і години. Наразі це план, не вже виконана розробка.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="46" customHeight="1">
+      <x:c r="A22" s="47" t="str">
+        <x:v>Як користуватися Excel</x:v>
+      </x:c>
+      <x:c r="B22" s="48" t="str">
+        <x:v>Підсумки — на аркуші «Підсумок». Підзадачі, джерела й передумови — на «Декомпозиція», зокрема колонки K/L. Жовті клітинки — вхідні оцінки. Формули змінювати не потрібно. Пропущений обов’язковий час дає #N/A; нуль допустимий.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="46" customHeight="1">
+      <x:c r="A23" s="47" t="str">
+        <x:v>Джерела методики</x:v>
+      </x:c>
+      <x:c r="B23" s="48" t="str">
+        <x:v>Аналіз коду від 22.10.2026, технічний документ №12; уточнення Supabase Auth і мобільного ярлика №15; для відкладених фіч — початкова декомпозиція №02. Це джерела планових припущень, а не дослідження продуктивності.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="25" customHeight="1">
+      <x:c r="A24" s="2"/>
+      <x:c r="B24" s="2"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/outputs/finance-hours-2026-10-22/finance-time-decomposition.xlsx
+++ b/outputs/finance-hours-2026-10-22/finance-time-decomposition.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Підсумок" sheetId="1" r:id="R9a41bba85e7c4716"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Декомпозиція" sheetId="2" r:id="R796b34f319a54438"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Методика" sheetId="3" r:id="R1ec2312ade8b4d45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Підсумок" sheetId="1" r:id="R93f0182c43054e1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Декомпозиція" sheetId="2" r:id="Rfbc1ed4451694848"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Методика" sheetId="3" r:id="R677a9c6bef994973"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -59,7 +59,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -91,8 +91,18 @@
         <x:fgColor rgb="FF233F5B"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF233F5B"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="3">
+  <x:borders count="4">
     <x:border>
       <x:left/>
       <x:right/>
@@ -118,11 +128,22 @@
       </x:bottom>
       <x:diagonal/>
     </x:border>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top style="thin">
+        <x:color rgb="FFD8E0E8"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD8E0E8"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="49">
+  <x:cellXfs count="63">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -266,10 +287,74 @@
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
+  <x:dxfs count="2">
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFB3261E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE8E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFB3261E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE8E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+  </x:dxfs>
 </x:styleSheet>
 </file>
 
@@ -538,7 +623,7 @@
     </x:row>
     <x:row r="3" ht="25" customHeight="1">
       <x:c r="A3" s="2" t="str">
-        <x:v>Планові оцінки на 22.10.2026. Години розробника, не фактично витрачений час.</x:v>
+        <x:v>Оцінки на 22.10.2026. План оновлено 25.10.2026: 18 год/тиждень протягом 12 тижнів.</x:v>
       </x:c>
       <x:c r="B3" s="2"/>
       <x:c r="C3" s="2"/>
@@ -663,7 +748,9 @@
       <x:c r="H7" s="2"/>
     </x:row>
     <x:row r="8" ht="25" customHeight="1">
-      <x:c r="A8" s="2"/>
+      <x:c r="A8" s="4" t="str">
+        <x:v>Погоджений обсяг: усі активні Must/Should/Could та P1. Розрахунок місткості — нижче.</x:v>
+      </x:c>
       <x:c r="B8" s="2"/>
       <x:c r="C8" s="2"/>
       <x:c r="D8" s="2"/>
@@ -1477,7 +1564,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="H46" s="34" t="str">
-        <x:v>Не входить у Must</x:v>
+        <x:v>У плані 12 тижнів</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="25" customHeight="1">
@@ -1580,10 +1667,428 @@
       <x:c r="G54" s="4"/>
       <x:c r="H54" s="4"/>
     </x:row>
+    <x:row r="57" ht="27" customHeight="1">
+      <x:c r="A57" s="3" t="str">
+        <x:v>Погоджений план на 12 тижнів</x:v>
+      </x:c>
+      <x:c r="B57" s="2"/>
+      <x:c r="C57" s="2"/>
+      <x:c r="D57" s="2"/>
+      <x:c r="E57" s="2"/>
+      <x:c r="F57" s="2"/>
+      <x:c r="G57" s="2"/>
+      <x:c r="H57" s="2"/>
+    </x:row>
+    <x:row r="58" ht="27" customHeight="1">
+      <x:c r="A58" s="4" t="str">
+        <x:v>Рішення користувачки від 25.10.2026. Дату старту ще не задано. Джерело: план ресурсу №17.</x:v>
+      </x:c>
+      <x:c r="B58" s="2"/>
+      <x:c r="C58" s="2"/>
+      <x:c r="D58" s="2"/>
+      <x:c r="E58" s="2"/>
+      <x:c r="F58" s="2"/>
+      <x:c r="G58" s="2"/>
+      <x:c r="H58" s="2"/>
+    </x:row>
+    <x:row r="59" ht="27" customHeight="1">
+      <x:c r="A59" s="2"/>
+      <x:c r="B59" s="2"/>
+      <x:c r="C59" s="2"/>
+      <x:c r="D59" s="2"/>
+      <x:c r="E59" s="2"/>
+      <x:c r="F59" s="2"/>
+      <x:c r="G59" s="2"/>
+      <x:c r="H59" s="2"/>
+    </x:row>
+    <x:row r="60" ht="27" customHeight="1">
+      <x:c r="A60" s="2" t="str">
+        <x:v>Тривалість, тижнів</x:v>
+      </x:c>
+      <x:c r="B60" s="50" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C60" s="2"/>
+      <x:c r="D60" s="2" t="str">
+        <x:v>Год/тиждень</x:v>
+      </x:c>
+      <x:c r="E60" s="50" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F60" s="2"/>
+      <x:c r="G60" s="2" t="str">
+        <x:v>Ресурс, год</x:v>
+      </x:c>
+      <x:c r="H60" s="35" t="n">
+        <x:f>IF(AND(COUNT(B60,E60)=2,B60&gt;0,E60&gt;0),B60*E60,NA())</x:f>
+        <x:v>216</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="27" customHeight="1">
+      <x:c r="A61" s="2" t="str">
+        <x:v>Резерв від ресурсу, год</x:v>
+      </x:c>
+      <x:c r="B61" s="2"/>
+      <x:c r="C61" s="2"/>
+      <x:c r="D61" s="2"/>
+      <x:c r="E61" s="35" t="n">
+        <x:f>IF(AND(COUNT(B10)=1,B10&gt;=0,B10&lt;1),H60*B10,NA())</x:f>
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F61" s="2"/>
+      <x:c r="G61" s="2"/>
+      <x:c r="H61" s="2"/>
+    </x:row>
+    <x:row r="62" ht="27" customHeight="1">
+      <x:c r="A62" s="2" t="str">
+        <x:v>Відома робота з P1, год</x:v>
+      </x:c>
+      <x:c r="B62" s="2"/>
+      <x:c r="C62" s="2"/>
+      <x:c r="D62" s="2"/>
+      <x:c r="E62" s="35" t="n">
+        <x:f>SUM(E7,G46)</x:f>
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="F62" s="2"/>
+      <x:c r="G62" s="2"/>
+      <x:c r="H62" s="2"/>
+    </x:row>
+    <x:row r="63" ht="27" customHeight="1">
+      <x:c r="A63" s="2" t="str">
+        <x:v>Мінімальний план із резервом, год</x:v>
+      </x:c>
+      <x:c r="B63" s="2"/>
+      <x:c r="C63" s="2"/>
+      <x:c r="D63" s="2"/>
+      <x:c r="E63" s="35" t="n">
+        <x:f>IF(AND(COUNT(B10)=1,B10&gt;=0,B10&lt;1),E62/(1-B10),NA())</x:f>
+        <x:v>209.33333333333334</x:v>
+      </x:c>
+      <x:c r="F63" s="2"/>
+      <x:c r="G63" s="2"/>
+      <x:c r="H63" s="2"/>
+    </x:row>
+    <x:row r="64" ht="27" customHeight="1">
+      <x:c r="A64" s="2" t="str">
+        <x:v>Резерв мінімального плану, год</x:v>
+      </x:c>
+      <x:c r="B64" s="2"/>
+      <x:c r="C64" s="2"/>
+      <x:c r="D64" s="2"/>
+      <x:c r="E64" s="35" t="n">
+        <x:f>E63-E62</x:f>
+        <x:v>52.33333333333334</x:v>
+      </x:c>
+      <x:c r="F64" s="2"/>
+      <x:c r="G64" s="2"/>
+      <x:c r="H64" s="2"/>
+    </x:row>
+    <x:row r="65" ht="27" customHeight="1">
+      <x:c r="A65" s="2" t="str">
+        <x:v>Вільно після роботи й резерву, год</x:v>
+      </x:c>
+      <x:c r="B65" s="2"/>
+      <x:c r="C65" s="2"/>
+      <x:c r="D65" s="2"/>
+      <x:c r="E65" s="35" t="n">
+        <x:f>H60-E62-E61</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F65" s="2"/>
+      <x:c r="G65" s="2"/>
+      <x:c r="H65" s="2"/>
+    </x:row>
+    <x:row r="66" ht="27" customHeight="1">
+      <x:c r="A66" s="2" t="str">
+        <x:v>Ресурс понад мінімальний план, год</x:v>
+      </x:c>
+      <x:c r="B66" s="2"/>
+      <x:c r="C66" s="2"/>
+      <x:c r="D66" s="2"/>
+      <x:c r="E66" s="35" t="n">
+        <x:f>H60-E63</x:f>
+        <x:v>6.666666666666657</x:v>
+      </x:c>
+      <x:c r="F66" s="2"/>
+      <x:c r="G66" s="2"/>
+      <x:c r="H66" s="2"/>
+    </x:row>
+    <x:row r="67" ht="27" customHeight="1">
+      <x:c r="A67" s="2"/>
+      <x:c r="B67" s="2"/>
+      <x:c r="C67" s="2"/>
+      <x:c r="D67" s="2"/>
+      <x:c r="E67" s="2"/>
+      <x:c r="F67" s="2"/>
+      <x:c r="G67" s="2"/>
+      <x:c r="H67" s="2"/>
+    </x:row>
+    <x:row r="68" ht="27" customHeight="1">
+      <x:c r="A68" s="4" t="str">
+        <x:v>Резерв місткості та резерв мінімального плану — два способи планування, їх не підсумовуємо.</x:v>
+      </x:c>
+      <x:c r="B68" s="4"/>
+      <x:c r="C68" s="4"/>
+      <x:c r="D68" s="4"/>
+      <x:c r="E68" s="4"/>
+      <x:c r="F68" s="4"/>
+      <x:c r="G68" s="4"/>
+      <x:c r="H68" s="4"/>
+    </x:row>
+    <x:row r="69" ht="27" customHeight="1">
+      <x:c r="A69" s="4" t="str">
+        <x:v>Власний час не монетизуємо. Грошовий кошторис залишається до $150 у межах $200.</x:v>
+      </x:c>
+      <x:c r="B69" s="4"/>
+      <x:c r="C69" s="4"/>
+      <x:c r="D69" s="4"/>
+      <x:c r="E69" s="4"/>
+      <x:c r="F69" s="4"/>
+      <x:c r="G69" s="4"/>
+      <x:c r="H69" s="4"/>
+    </x:row>
+    <x:row r="70" ht="27" customHeight="1">
+      <x:c r="A70" s="2"/>
+      <x:c r="B70" s="2"/>
+      <x:c r="C70" s="2"/>
+      <x:c r="D70" s="2"/>
+      <x:c r="E70" s="2"/>
+      <x:c r="F70" s="2"/>
+      <x:c r="G70" s="2"/>
+      <x:c r="H70" s="2"/>
+    </x:row>
+    <x:row r="71" ht="27" customHeight="1">
+      <x:c r="A71" s="3" t="str">
+        <x:v>Розподіл роботи за місяцями</x:v>
+      </x:c>
+      <x:c r="B71" s="2"/>
+      <x:c r="C71" s="2"/>
+      <x:c r="D71" s="2"/>
+      <x:c r="E71" s="2"/>
+      <x:c r="F71" s="2"/>
+      <x:c r="G71" s="2"/>
+      <x:c r="H71" s="2"/>
+    </x:row>
+    <x:row r="72" ht="34" customHeight="1">
+      <x:c r="A72" s="54" t="str">
+        <x:v>Місяць</x:v>
+      </x:c>
+      <x:c r="B72" s="54" t="str">
+        <x:v>Тижнів</x:v>
+      </x:c>
+      <x:c r="C72" s="54" t="str">
+        <x:v>Ресурс, год</x:v>
+      </x:c>
+      <x:c r="D72" s="54" t="str">
+        <x:v>Робота, год</x:v>
+      </x:c>
+      <x:c r="E72" s="54" t="str">
+        <x:v>Резерв, год</x:v>
+      </x:c>
+      <x:c r="F72" s="54" t="str">
+        <x:v>Вільно, год</x:v>
+      </x:c>
+      <x:c r="G72" s="54" t="str">
+        <x:v>Год/тиждень</x:v>
+      </x:c>
+      <x:c r="H72" s="54" t="str">
+        <x:v>Пакет</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="44" customHeight="1">
+      <x:c r="A73" s="2" t="str">
+        <x:v>Місяць 1</x:v>
+      </x:c>
+      <x:c r="B73" s="10" t="n">
+        <x:f>$B$60/3</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C73" s="10" t="n">
+        <x:f>B73*$E$60</x:f>
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D73" s="10" t="n">
+        <x:f>SUM(G42,G18,G20,'Декомпозиція'!H29,'Декомпозиція'!H30,'Декомпозиція'!H32)</x:f>
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E73" s="10" t="n">
+        <x:f>C73*$B$10</x:f>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F73" s="10" t="n">
+        <x:f>C73-D73-E73</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G73" s="10" t="n">
+        <x:f>$E$60</x:f>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H73" s="9" t="str">
+        <x:v>S0, №2/9, частина №12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="44" customHeight="1">
+      <x:c r="A74" s="2" t="str">
+        <x:v>Місяць 2</x:v>
+      </x:c>
+      <x:c r="B74" s="10" t="n">
+        <x:f>$B$60/3</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C74" s="10" t="n">
+        <x:f>B74*$E$60</x:f>
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D74" s="10" t="n">
+        <x:f>SUM(G21,G22,G19,G46,G43)-SUM('Декомпозиція'!H29,'Декомпозиція'!H30,'Декомпозиція'!H32)</x:f>
+        <x:v>50.5</x:v>
+      </x:c>
+      <x:c r="E74" s="10" t="n">
+        <x:f>C74*$B$10</x:f>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F74" s="10" t="n">
+        <x:f>C74-D74-E74</x:f>
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="G74" s="10" t="n">
+        <x:f>$E$60</x:f>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H74" s="9" t="str">
+        <x:v>Решта Must, P1, G-M</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="44" customHeight="1">
+      <x:c r="A75" s="2" t="str">
+        <x:v>Місяць 3</x:v>
+      </x:c>
+      <x:c r="B75" s="10" t="n">
+        <x:f>$B$60/3</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C75" s="10" t="n">
+        <x:f>B75*$E$60</x:f>
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D75" s="10" t="n">
+        <x:f>SUM(D6:D7)</x:f>
+        <x:v>52.5</x:v>
+      </x:c>
+      <x:c r="E75" s="10" t="n">
+        <x:f>C75*$B$10</x:f>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F75" s="10" t="n">
+        <x:f>C75-D75-E75</x:f>
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="G75" s="10" t="n">
+        <x:f>$E$60</x:f>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H75" s="9" t="str">
+        <x:v>Should, Could, G-S/G-C</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="27" customHeight="1">
+      <x:c r="A76" s="55" t="str">
+        <x:v>Разом</x:v>
+      </x:c>
+      <x:c r="B76" s="56" t="n">
+        <x:f>SUM(B73:B75)</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C76" s="56" t="n">
+        <x:f>SUM(C73:C75)</x:f>
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="D76" s="56" t="n">
+        <x:f>SUM(D73:D75)</x:f>
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="E76" s="56" t="n">
+        <x:f>SUM(E73:E75)</x:f>
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F76" s="56" t="n">
+        <x:f>SUM(F73:F75)</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G76" s="56"/>
+      <x:c r="H76" s="55" t="str">
+        <x:v>Усі активні та P1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="27" customHeight="1">
+      <x:c r="A77" s="2"/>
+      <x:c r="B77" s="2"/>
+      <x:c r="C77" s="2"/>
+      <x:c r="D77" s="2"/>
+      <x:c r="E77" s="2"/>
+      <x:c r="F77" s="2"/>
+      <x:c r="G77" s="2"/>
+      <x:c r="H77" s="2"/>
+    </x:row>
+    <x:row r="78" ht="27" customHeight="1">
+      <x:c r="A78" s="4" t="str">
+        <x:v>Місяці — три рівні частини 12-тижневого плану. Негативний залишок означає дефіцит місткості.</x:v>
+      </x:c>
+      <x:c r="B78" s="4"/>
+      <x:c r="C78" s="4"/>
+      <x:c r="D78" s="4"/>
+      <x:c r="E78" s="4"/>
+      <x:c r="F78" s="4"/>
+      <x:c r="G78" s="4"/>
+      <x:c r="H78" s="4"/>
+    </x:row>
+    <x:row r="79" ht="27" customHeight="1">
+      <x:c r="A79" s="4" t="str">
+        <x:v>У місяці 1: №12.1 + №12.2 + №12.4. Публічний доступ після повних перевірок у місяці 2.</x:v>
+      </x:c>
+      <x:c r="B79" s="4"/>
+      <x:c r="C79" s="4"/>
+      <x:c r="D79" s="4"/>
+      <x:c r="E79" s="4"/>
+      <x:c r="F79" s="4"/>
+      <x:c r="G79" s="4"/>
+      <x:c r="H79" s="4"/>
+    </x:row>
+    <x:row r="80" ht="27" customHeight="1">
+      <x:c r="A80" s="4" t="str">
+        <x:v>Після ядра: №5, потім №21/10, далі №14/8/3. Won’t відкладені; за перевитрат першими переносимо Could.</x:v>
+      </x:c>
+      <x:c r="B80" s="4"/>
+      <x:c r="C80" s="4"/>
+      <x:c r="D80" s="4"/>
+      <x:c r="E80" s="4"/>
+      <x:c r="F80" s="4"/>
+      <x:c r="G80" s="4"/>
+      <x:c r="H80" s="4"/>
+    </x:row>
   </x:sheetData>
+  <x:conditionalFormatting sqref="E65:E65">
+    <x:cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+      <x:formula>0</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="F73:F75">
+    <x:cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
+      <x:formula>0</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:dataValidations count="2">
+    <x:dataValidation type="decimal" operator="greaterThan" sqref="B60">
+      <x:formula1>0</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="greaterThan" sqref="E60">
+      <x:formula1>0</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1f61ec0353a493f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R716ad8907005498e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5669,7 +6174,7 @@
         <x:v>Аналіз коду №12, P1.1</x:v>
       </x:c>
       <x:c r="L121" s="9" t="str">
-        <x:v>Окрема вимога PRD щодо періодів Олі між зарплатами; не входить у календарні Must.</x:v>
+        <x:v>Окремий блок зарплатних періодів Олі. Входить до погодженого 12-тижневого плану, але не до календарних Must.</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="38" customHeight="1">
@@ -5704,7 +6209,7 @@
         <x:v>Аналіз коду №12, P1.2</x:v>
       </x:c>
       <x:c r="L122" s="9" t="str">
-        <x:v>Окрема вимога PRD щодо періодів Олі між зарплатами; не входить у календарні Must.</x:v>
+        <x:v>Окремий блок зарплатних періодів Олі. Входить до погодженого 12-тижневого плану, але не до календарних Must.</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="38" customHeight="1">
@@ -5739,7 +6244,7 @@
         <x:v>Аналіз коду №12, P1.3</x:v>
       </x:c>
       <x:c r="L123" s="9" t="str">
-        <x:v>Окрема вимога PRD щодо періодів Олі між зарплатами; не входить у календарні Must.</x:v>
+        <x:v>Окремий блок зарплатних періодів Олі. Входить до погодженого 12-тижневого плану, але не до календарних Must.</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="38" customHeight="1">
@@ -5774,13 +6279,13 @@
         <x:v>Аналіз коду №12, P1.4</x:v>
       </x:c>
       <x:c r="L124" s="9" t="str">
-        <x:v>Окрема вимога PRD щодо періодів Олі між зарплатами; не входить у календарні Must.</x:v>
+        <x:v>Окремий блок зарплатних періодів Олі. Входить до погодженого 12-тижневого плану, але не до календарних Must.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c7b91f14fcf4629"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ec443a1cb7d4006"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5968,9 +6473,29 @@
         <x:v>Аналіз коду від 22.10.2026, технічний документ №12; уточнення Supabase Auth і мобільного ярлика №15; для відкладених фіч — початкова декомпозиція №02. Це джерела планових припущень, а не дослідження продуктивності.</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="25" customHeight="1">
-      <x:c r="A24" s="2"/>
-      <x:c r="B24" s="2"/>
+    <x:row r="24" ht="72" customHeight="1">
+      <x:c r="A24" s="47" t="str">
+        <x:v>Погоджений ресурс</x:v>
+      </x:c>
+      <x:c r="B24" s="48" t="str">
+        <x:v>25.10.2026 погоджено 18 год/тиждень протягом 12 тижнів на всі активні фічі та P1. Тривалість і години — жовті входи на «Підсумок», B60/E60. Оцінки підзадач не змінено.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="72" customHeight="1">
+      <x:c r="A25" s="60" t="str">
+        <x:v>Місткість і резерв</x:v>
+      </x:c>
+      <x:c r="B25" s="61" t="str">
+        <x:v>На «Підсумок», E62 — усі активні плюс P1; H60 — тижні × години. E61 — частка резерву від місткості, E65 — вільно після роботи й резерву. E63 — мінімальний план із пропорційним резервом. Ці резерви не додаємо один до одного.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="72" customHeight="1">
+      <x:c r="A26" s="62" t="str">
+        <x:v>Календар і контроль</x:v>
+      </x:c>
+      <x:c r="B26" s="16" t="str">
+        <x:v>Місячний розподіл на «Підсумок», рядки 73–76, посилається на години фіч і спільних блоків. Частину №12 перенесено в місяць 1 без повторного рахунку. Щотижня звіряємо фактичні години з планом; негативний залишок означає дефіцит. Джерело: план ресурсу №17.</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
